--- a/AtchisonRegime/Outputs/USA/USA_Low_Volatility/df_regSummary_USA_Low_Volatility.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Low_Volatility/df_regSummary_USA_Low_Volatility.xlsx
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>1.351951188266407</v>
+        <v>1.121544945711472</v>
       </c>
       <c r="H2" t="n">
-        <v>3.264579378436513</v>
+        <v>3.561807350733982</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.41020346327878</v>
+        <v>-8.555517241595799</v>
       </c>
       <c r="J2" t="n">
         <v>7.36666934510836</v>
       </c>
       <c r="K2" t="n">
-        <v>32.55813953488372</v>
+        <v>33.07692307692307</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1237357192886825</v>
+        <v>0.09954799099203782</v>
       </c>
       <c r="O2" t="n">
         <v>-0.01152848052935629</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4135748671656625</v>
+        <v>0.2926362256824393</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>7.93887645673724</v>
       </c>
       <c r="K3" t="n">
-        <v>20.15503875968992</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>8.375876401854281</v>
       </c>
       <c r="K4" t="n">
-        <v>22.48062015503876</v>
+        <v>22.30769230769231</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>6.87229435690348</v>
       </c>
       <c r="K5" t="n">
-        <v>24.8062015503876</v>
+        <v>24.61538461538462</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
